--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260727_210030.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260727_210030.xlsx
@@ -6408,7 +6408,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260727_210030.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260727_210030.xlsx
@@ -6408,7 +6408,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
